--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B534B74B-20EA-4B00-AC9A-46BF455B0E15}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>very tired after classes</t>
   </si>
 </sst>
 </file>
@@ -396,8 +402,8 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,6 +500,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -902,35 +912,35 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12610019</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -1041,26 +1051,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>100</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>480</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
+        <v>45</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>245</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B534B74B-20EA-4B00-AC9A-46BF455B0E15}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{062FF1DC-B33F-4AE0-8F0B-FF65434BCECE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>very tired after classes</t>
+  </si>
+  <si>
+    <t>2026-008-26</t>
   </si>
 </sst>
 </file>
@@ -1097,26 +1100,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="14">
+        <v>500</v>
+      </c>
+      <c r="C8" s="14">
+        <v>25</v>
+      </c>
+      <c r="D8" s="14">
+        <v>90</v>
+      </c>
+      <c r="E8" s="14">
+        <v>70</v>
+      </c>
+      <c r="F8" s="14">
+        <v>480</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>45</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{062FF1DC-B33F-4AE0-8F0B-FF65434BCECE}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C82FA591-94A2-45C3-90DD-CF589D47DE2D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1146,26 +1146,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>100</v>
+      </c>
+      <c r="E9" s="14">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14">
+        <v>430</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>50</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C82FA591-94A2-45C3-90DD-CF589D47DE2D}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABEA4321-F056-4C39-92FF-A0D82ABD0E2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>2026-008-26</t>
+  </si>
+  <si>
+    <t>26-08-28</t>
   </si>
 </sst>
 </file>
@@ -1192,26 +1195,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>340</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>40</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABEA4321-F056-4C39-92FF-A0D82ABD0E2F}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E15E0CA-D68B-4A04-981E-F76360CB4503}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1241,26 +1241,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B11" s="14">
+        <v>520</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>100</v>
+      </c>
+      <c r="E11" s="14">
+        <v>50</v>
+      </c>
+      <c r="F11" s="14">
+        <v>430</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>45</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E15E0CA-D68B-4A04-981E-F76360CB4503}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D51112E-0668-4461-9764-BDE256DD5105}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>26-08-28</t>
+  </si>
+  <si>
+    <t>feeling good</t>
   </si>
 </sst>
 </file>
@@ -1287,26 +1290,48 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="A12" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>250</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
       <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D51112E-0668-4461-9764-BDE256DD5105}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE0FD8A9-5E81-4973-A50B-B066C21A8E24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>feeling good</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -1334,26 +1337,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>430</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE0FD8A9-5E81-4973-A50B-B066C21A8E24}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11FDB639-A5FC-4DEE-8E07-F5F1FCD8F2C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>tired after class</t>
   </si>
 </sst>
 </file>
@@ -1383,26 +1389,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>25</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>70</v>
+      </c>
+      <c r="F14" s="14">
+        <v>480</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>45</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11FDB639-A5FC-4DEE-8E07-F5F1FCD8F2C9}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FE0F3D-3CFE-4726-903B-961A72A321D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1317,7 +1317,9 @@
       <c r="F12" s="14">
         <v>0</v>
       </c>
-      <c r="G12" s="14"/>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
       <c r="H12" s="14">
         <v>120</v>
       </c>
@@ -1435,7 +1437,9 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13">
+        <v>46266</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FE0F3D-3CFE-4726-903B-961A72A321D7}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71058F09-9802-4C5E-BA6E-1052087F163B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>tired after class</t>
+  </si>
+  <si>
+    <t>20026-09-04</t>
   </si>
 </sst>
 </file>
@@ -1438,71 +1441,141 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46266</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>46267</v>
+      </c>
+      <c r="B15" s="14">
+        <v>460</v>
+      </c>
+      <c r="C15" s="14">
+        <v>25</v>
+      </c>
+      <c r="D15" s="14">
+        <v>170</v>
+      </c>
+      <c r="E15" s="14">
+        <v>80</v>
+      </c>
+      <c r="F15" s="14">
+        <v>430</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>70</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>205</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B16" s="14">
+        <v>470</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>160</v>
+      </c>
+      <c r="E16" s="14">
+        <v>85</v>
+      </c>
+      <c r="F16" s="14">
+        <v>450</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1255</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>185</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>25</v>
+      </c>
+      <c r="D17" s="14">
+        <v>150</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
+      <c r="F17" s="14">
+        <v>450</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>50</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>195</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71058F09-9802-4C5E-BA6E-1052087F163B}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F703E3-EFED-4DBB-9085-3BC4697E01A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1578,26 +1578,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B18" s="14">
+        <v>500</v>
+      </c>
+      <c r="C18" s="14">
+        <v>25</v>
+      </c>
+      <c r="D18" s="14">
+        <v>170</v>
+      </c>
+      <c r="E18" s="14">
+        <v>90</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F703E3-EFED-4DBB-9085-3BC4697E01A7}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{011DC9C6-7E01-4D72-926C-09643FE1998E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1624,26 +1624,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B19" s="14">
+        <v>600</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>180</v>
+      </c>
+      <c r="E19" s="14">
+        <v>110</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{011DC9C6-7E01-4D72-926C-09643FE1998E}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{400FE3CD-9A82-4BC7-BBD6-77B876C9CC17}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1670,26 +1670,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>45</v>
+      </c>
+      <c r="F20" s="14">
+        <v>480</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{400FE3CD-9A82-4BC7-BBD6-77B876C9CC17}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B4A01D-BB5E-41F9-BD80-8C8FB007CC8B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1716,26 +1716,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B21" s="14">
+        <v>440</v>
+      </c>
+      <c r="C21" s="14">
+        <v>23</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>45</v>
+      </c>
+      <c r="F21" s="14">
+        <v>480</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1108</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>332</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B4A01D-BB5E-41F9-BD80-8C8FB007CC8B}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511593F8-FC50-4FAE-91E8-C0500B9A02AC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1762,26 +1762,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>25</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>360</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1255</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>185</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
